--- a/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:40:33+00:00</t>
+    <t>2026-07-21T12:38:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:38:43+00:00</t>
+    <t>2026-07-21T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:31+00:00</t>
+    <t>2026-07-21T13:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/main/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:21:42+00:00</t>
+    <t>2026-07-21T13:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
